--- a/DocumentaciónMER.xlsx
+++ b/DocumentaciónMER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Desktop\DOO\DOO\Barberia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/120f6d501c463b80/Escritorio/leo/Doo/Barberia proyecto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450A1BB8-17E4-4668-8335-5813D3BA392C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{450A1BB8-17E4-4668-8335-5813D3BA392C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15834F25-7ACF-4324-9CDD-E955DBB4EC81}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="9" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MER" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <sheet name="Multa" sheetId="17" r:id="rId17"/>
     <sheet name="Valores" sheetId="18" state="hidden" r:id="rId18"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1189,7 +1189,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1220,51 +1220,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1277,6 +1232,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1286,11 +1261,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1681,11 +1678,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" style="8" customWidth="1"/>
-    <col min="3" max="16384" width="11.44140625" style="8"/>
+    <col min="1" max="1" width="24.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1696,150 +1693,150 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.77734375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A9</f>
         <v>HorarioBarberia</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B9</f>
         <v>Entidad que registra, día por día, la hora de apertura y de cierre de la barbería, que es el límite dentro del cual debe caber el horario de cualquier barbero.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -1870,10 +1867,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1915,11 +1912,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>129</v>
       </c>
@@ -1965,11 +1962,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>132</v>
       </c>
@@ -2009,11 +2006,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>135</v>
       </c>
@@ -2053,11 +2050,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>137</v>
       </c>
@@ -2097,11 +2094,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>140</v>
       </c>
@@ -2141,11 +2138,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>104</v>
       </c>
@@ -2185,12 +2182,14 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>142</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -2207,8 +2206,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
@@ -2220,150 +2217,150 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A10</f>
         <v>Bloqueo</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="34" t="str">
+      <c r="B3" s="43" t="str">
         <f>Entidades!B10</f>
         <v>Entidad que registra los rangos de fecha y hora en los que un barbero no está disponible para atender sus citas.</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2394,10 +2391,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -2439,11 +2436,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>144</v>
       </c>
@@ -2489,11 +2486,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>147</v>
       </c>
@@ -2533,11 +2530,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>150</v>
       </c>
@@ -2577,12 +2574,14 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>151</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -2599,8 +2598,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
@@ -2612,150 +2609,150 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A11</f>
         <v>BarberoServicio</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B11</f>
         <v>Entidad asociativa que registra qué servicios sabe hacer cada barbero, cuánto tarda en realizarlos y cuánto tiempo extra reserva para ellos.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2786,10 +2783,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -2831,11 +2828,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>144</v>
       </c>
@@ -2881,11 +2878,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>155</v>
       </c>
@@ -2931,11 +2928,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>157</v>
       </c>
@@ -2977,11 +2974,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>160</v>
       </c>
@@ -3023,11 +3020,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>163</v>
       </c>
@@ -3069,11 +3066,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>104</v>
       </c>
@@ -3111,12 +3108,14 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -3133,8 +3132,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
@@ -3146,150 +3143,150 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:T14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A12</f>
         <v>HorarioBarbero</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="28.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B12</f>
         <v>Entidad que registra la jornada de trabajo de un barbero dentro de un horario de la barbería, con la hora en la que empieza, la hora en la que termina y su vigencia.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -3320,10 +3317,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -3365,11 +3362,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>144</v>
       </c>
@@ -3415,11 +3412,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>170</v>
       </c>
@@ -3465,11 +3462,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>172</v>
       </c>
@@ -3509,11 +3506,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>174</v>
       </c>
@@ -3553,11 +3550,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>137</v>
       </c>
@@ -3595,11 +3592,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>140</v>
       </c>
@@ -3637,11 +3634,11 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>104</v>
       </c>
@@ -3679,12 +3676,14 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="T14" s="35" t="s">
+      <c r="T14" s="12" t="s">
         <v>177</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -3701,8 +3700,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
@@ -3714,150 +3711,150 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A13</f>
         <v>Agenda</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="34" t="str">
+      <c r="B3" s="43" t="str">
         <f>Entidades!B13</f>
         <v>Entidad que representa el día concreto de trabajo de un barbero, según su horario, en el que se agrupan todas las citas de ese día.</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -3888,10 +3885,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -3933,11 +3930,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>179</v>
       </c>
@@ -3983,11 +3980,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>182</v>
       </c>
@@ -4027,12 +4024,14 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>183</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -4049,8 +4048,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
@@ -4062,150 +4059,150 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.5703125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A14</f>
         <v>Cita</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B14</f>
         <v>Entidad que registra la reserva de un cliente con un barbero para una fecha y hora concretas, con su estado, los tiempos reales de la atención y el valor que debe pagar el cliente.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -4236,10 +4233,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -4281,11 +4278,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>185</v>
       </c>
@@ -4329,11 +4326,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>187</v>
       </c>
@@ -4379,11 +4376,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>190</v>
       </c>
@@ -4427,11 +4424,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>172</v>
       </c>
@@ -4471,11 +4468,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>193</v>
       </c>
@@ -4513,11 +4510,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>195</v>
       </c>
@@ -4555,11 +4552,11 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>197</v>
       </c>
@@ -4597,11 +4594,11 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="T14" s="35" t="s">
+      <c r="T14" s="12" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>199</v>
       </c>
@@ -4639,11 +4636,11 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="T15" s="35" t="s">
+      <c r="T15" s="12" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>201</v>
       </c>
@@ -4681,11 +4678,11 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="T16" s="35" t="s">
+      <c r="T16" s="12" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>203</v>
       </c>
@@ -4727,11 +4724,11 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
-      <c r="T17" s="35" t="s">
+      <c r="T17" s="12" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>206</v>
       </c>
@@ -4773,11 +4770,11 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
-      <c r="T18" s="35" t="s">
+      <c r="T18" s="12" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>209</v>
       </c>
@@ -4819,11 +4816,11 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
-      <c r="T19" s="35" t="s">
+      <c r="T19" s="12" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>212</v>
       </c>
@@ -4865,11 +4862,11 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="T20" s="35" t="s">
+      <c r="T20" s="12" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>215</v>
       </c>
@@ -4911,11 +4908,11 @@
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
-      <c r="T21" s="35" t="s">
+      <c r="T21" s="12" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>218</v>
       </c>
@@ -4957,11 +4954,11 @@
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
-      <c r="T22" s="35" t="s">
+      <c r="T22" s="12" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>221</v>
       </c>
@@ -5003,11 +5000,11 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
-      <c r="T23" s="35" t="s">
+      <c r="T23" s="12" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>224</v>
       </c>
@@ -5049,12 +5046,14 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
-      <c r="T24" s="35" t="s">
+      <c r="T24" s="12" t="s">
         <v>226</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -5071,8 +5070,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
@@ -5084,150 +5081,150 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.88671875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A15</f>
         <v>CitaServicio</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B15</f>
         <v>Entidad asociativa que registra cada servicio incluido dentro de una cita, congelando el precio y la duración que tenía ese servicio para ese barbero en el momento de agendarla.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -5258,10 +5255,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -5303,11 +5300,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>228</v>
       </c>
@@ -5353,11 +5350,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>231</v>
       </c>
@@ -5403,11 +5400,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>233</v>
       </c>
@@ -5449,11 +5446,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>236</v>
       </c>
@@ -5495,11 +5492,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>239</v>
       </c>
@@ -5541,11 +5538,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>163</v>
       </c>
@@ -5587,12 +5584,14 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>243</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -5609,8 +5608,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
@@ -5622,150 +5619,150 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A16</f>
         <v>Multa</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B16</f>
         <v>Entidad que registra la sanción económica impuesta a un cliente por incumplir una cita, ya sea por tardanza o por inasistencia, con su monto y su estado de pago.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -5796,10 +5793,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -5841,11 +5838,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>228</v>
       </c>
@@ -5891,11 +5888,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>247</v>
       </c>
@@ -5939,11 +5936,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>249</v>
       </c>
@@ -5985,11 +5982,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>252</v>
       </c>
@@ -6027,11 +6024,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>254</v>
       </c>
@@ -6069,11 +6066,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>256</v>
       </c>
@@ -6111,12 +6108,14 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>257</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -6133,8 +6132,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
@@ -6146,13 +6143,13 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>258</v>
       </c>
@@ -6166,7 +6163,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>261</v>
       </c>
@@ -6180,7 +6177,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>264</v>
       </c>
@@ -6199,13 +6196,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
@@ -6213,123 +6210,123 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="37" t="s">
+      <c r="B4" s="14" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="14" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="38" t="s">
+      <c r="B10" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="38" t="s">
+      <c r="B11" s="15" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B12" s="38" t="s">
+      <c r="B12" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="38" t="s">
+      <c r="B13" s="15" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="38" t="s">
+      <c r="B14" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="B15" s="38" t="s">
+      <c r="B15" s="15" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="38" t="s">
+      <c r="B16" s="15" t="s">
         <v>66</v>
       </c>
     </row>
@@ -6342,150 +6339,150 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="54.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="54.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A2</f>
         <v>DiaSemana</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="19" t="str">
+      <c r="B3" s="38" t="str">
         <f>Entidades!B2</f>
         <v>Catálogo de los días de la semana, incluido festivo, que se usan para definir los horarios de la barbería y de cada barbero.</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="15"/>
-      <c r="T4" s="16"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="B4" s="35"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="36"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="15"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="12" t="s">
+      <c r="J5" s="35"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="16"/>
-      <c r="N5" s="12" t="s">
+      <c r="M5" s="36"/>
+      <c r="N5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="16"/>
-      <c r="P5" s="12" t="s">
+      <c r="O5" s="36"/>
+      <c r="P5" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="12" t="s">
+      <c r="Q5" s="35"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="T5" s="37" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -6516,10 +6513,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>26</v>
       </c>
@@ -6565,7 +6562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -6607,12 +6604,14 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="I5:K5"/>
     <mergeCell ref="A1:E1"/>
@@ -6629,8 +6628,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -6642,150 +6639,150 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="45" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A3</f>
         <v>Estado</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B3</f>
         <v>Catálogo de los estados en los que puede encontrarse una cita durante su ciclo de vida: agendada, finalizada, cancelada, con tardanza o con inasistencia.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -6816,10 +6813,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -6861,11 +6858,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="36" t="s">
+      <c r="T7" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -6907,11 +6904,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="36" t="s">
+      <c r="T8" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>70</v>
       </c>
@@ -6951,12 +6948,14 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="36" t="s">
+      <c r="T9" s="13" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -6973,8 +6972,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -6986,150 +6983,150 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.33203125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.28515625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A4</f>
         <v>Servicio</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B4</f>
         <v>Entidad que almacena los servicios de corte y arreglo que ofrece la barbería, definidos por el dueño, y que luego cada barbero decide si los habilita.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -7160,10 +7157,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -7205,11 +7202,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -7251,11 +7248,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -7295,11 +7292,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>76</v>
       </c>
@@ -7341,11 +7338,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -7383,12 +7380,14 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -7405,8 +7404,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -7418,150 +7415,150 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A5</f>
         <v>PrefijoCelular</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="19" t="str">
+      <c r="B3" s="38" t="str">
         <f>Entidades!B5</f>
         <v>Catálogo de prefijos telefónicos de país disponibles para el número de celular de barberos y clientes.</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="40"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="43"/>
-      <c r="S4" s="43"/>
-      <c r="T4" s="43"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="42"/>
+      <c r="L4" s="42"/>
+      <c r="M4" s="42"/>
+      <c r="N4" s="42"/>
+      <c r="O4" s="42"/>
+      <c r="P4" s="42"/>
+      <c r="Q4" s="42"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="43"/>
-      <c r="K5" s="43"/>
-      <c r="L5" s="12" t="s">
+      <c r="J5" s="42"/>
+      <c r="K5" s="42"/>
+      <c r="L5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="43"/>
-      <c r="N5" s="12" t="s">
+      <c r="M5" s="42"/>
+      <c r="N5" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="43"/>
-      <c r="P5" s="12" t="s">
+      <c r="O5" s="42"/>
+      <c r="P5" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="43"/>
-      <c r="R5" s="43"/>
-      <c r="S5" s="12" t="s">
+      <c r="Q5" s="42"/>
+      <c r="R5" s="42"/>
+      <c r="S5" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="12" t="s">
+      <c r="T5" s="37" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -7592,10 +7589,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="43"/>
-      <c r="T6" s="43"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="42"/>
+      <c r="T6" s="42"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -7637,11 +7634,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>84</v>
       </c>
@@ -7683,56 +7680,15 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="42"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="42"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="42"/>
-    </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -7749,8 +7705,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -7762,150 +7716,150 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.5546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.5703125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A6</f>
         <v>TipoMulta</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="34" t="str">
+      <c r="B3" s="43" t="str">
         <f>Entidades!B6</f>
         <v>Catálogo de los tipos de multa que se le pueden imponer a un cliente: por tardanza o por inasistencia.</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -7936,10 +7890,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -7981,11 +7935,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="36" t="s">
+      <c r="T7" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -8027,11 +7981,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="36" t="s">
+      <c r="T8" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -8071,34 +8025,15 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="42"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="42"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="42"/>
-    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -8115,8 +8050,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -8128,150 +8061,150 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:T16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A7</f>
         <v>Barbero</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="39" t="str">
+      <c r="B3" s="28" t="str">
         <f>Entidades!B7</f>
         <v>Entidad que almacena la información de los barberos que trabajan en la barbería, con su contacto, su vigencia y la anticipación mínima que exigen para que les agenden una cita.</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="41"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -8302,10 +8235,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -8347,11 +8280,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>92</v>
       </c>
@@ -8391,11 +8324,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -8435,11 +8368,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>96</v>
       </c>
@@ -8479,11 +8412,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>98</v>
       </c>
@@ -8523,11 +8456,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>84</v>
       </c>
@@ -8573,11 +8506,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -8619,11 +8552,11 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>104</v>
       </c>
@@ -8661,11 +8594,11 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="T14" s="35" t="s">
+      <c r="T14" s="12" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>106</v>
       </c>
@@ -8707,11 +8640,11 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="T15" s="35" t="s">
+      <c r="T15" s="12" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -8753,12 +8686,14 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="T16" s="35" t="s">
+      <c r="T16" s="12" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -8775,8 +8710,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
@@ -8788,150 +8721,150 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:T16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32.88671875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.6640625" style="1"/>
+    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-    </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+    </row>
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="22" t="str">
+      <c r="B2" s="25" t="str">
         <f>Entidades!A8</f>
         <v>Cliente</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="34" t="str">
+      <c r="B3" s="43" t="str">
         <f>Entidades!B8</f>
         <v>Entidad que almacena la información de los clientes que solicitan citas en la barbería, junto con sus multas sin pagar y su estado de veto.</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="30"/>
-      <c r="J4" s="30"/>
-      <c r="K4" s="30"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="30"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30"/>
-      <c r="P4" s="30"/>
-      <c r="Q4" s="30"/>
-      <c r="R4" s="30"/>
-      <c r="S4" s="30"/>
-      <c r="T4" s="31"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="18"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="27" t="s">
+      <c r="I5" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="23"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="27" t="s">
+      <c r="J5" s="21"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="24"/>
-      <c r="N5" s="27" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="24"/>
-      <c r="P5" s="27" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="27" t="s">
+      <c r="Q5" s="21"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="32" t="s">
+      <c r="T5" s="26" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="32"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -8962,10 +8895,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="13"/>
-      <c r="T6" s="33"/>
-    </row>
-    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="S6" s="24"/>
+      <c r="T6" s="27"/>
+    </row>
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -9007,11 +8940,11 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
-      <c r="T7" s="35" t="s">
+      <c r="T7" s="12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>92</v>
       </c>
@@ -9051,11 +8984,11 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
-      <c r="T8" s="35" t="s">
+      <c r="T8" s="12" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -9095,11 +9028,11 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="12" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>96</v>
       </c>
@@ -9139,11 +9072,11 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
-      <c r="T10" s="35" t="s">
+      <c r="T10" s="12" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>98</v>
       </c>
@@ -9183,11 +9116,11 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
-      <c r="T11" s="35" t="s">
+      <c r="T11" s="12" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>117</v>
       </c>
@@ -9233,11 +9166,11 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
-      <c r="T12" s="35" t="s">
+      <c r="T12" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -9279,11 +9212,11 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
-      <c r="T13" s="35" t="s">
+      <c r="T13" s="12" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>121</v>
       </c>
@@ -9321,11 +9254,11 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
-      <c r="T14" s="35" t="s">
+      <c r="T14" s="12" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>123</v>
       </c>
@@ -9367,11 +9300,11 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
-      <c r="T15" s="35" t="s">
+      <c r="T15" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>126</v>
       </c>
@@ -9409,12 +9342,14 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="T16" s="35" t="s">
+      <c r="T16" s="12" t="s">
         <v>127</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
@@ -9431,8 +9366,6 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0800-000000000000}"/>

--- a/DocumentaciónMER.xlsx
+++ b/DocumentaciónMER.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/120f6d501c463b80/Escritorio/leo/Doo/Barberia proyecto/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Desktop\Proyecto agendamiento citas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{450A1BB8-17E4-4668-8335-5813D3BA392C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15834F25-7ACF-4324-9CDD-E955DBB4EC81}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22064AE6-D91D-4AB7-BCA1-BA685635D180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MER" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="263">
   <si>
     <t>&lt;-Volver al inicio</t>
   </si>
@@ -419,15 +419,6 @@
   </si>
   <si>
     <t>Indica si el número de celular que registró el cliente es correcto.</t>
-  </si>
-  <si>
-    <t>multasSinPagar</t>
-  </si>
-  <si>
-    <t>CHK_cliente_multasSinPagar</t>
-  </si>
-  <si>
-    <t>Cantidad de multas que el cliente tiene sin pagar. Debe estar entre 0 y 1.</t>
   </si>
   <si>
     <t>estaVetado</t>
@@ -1232,26 +1223,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1268,22 +1266,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1311,22 +1302,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>2880</xdr:colOff>
+      <xdr:colOff>206829</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:rowOff>98393</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D43ADF32-3496-2859-48E3-0F163D014EEB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1335,22 +1326,25 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="16560051" cy="7123611"/>
+          <a:off x="1" y="1"/>
+          <a:ext cx="16763999" cy="7130563"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-        <a:ln>
-          <a:prstDash val="solid"/>
-        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1678,11 +1672,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="8" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="8"/>
+    <col min="1" max="1" width="24.33203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" style="8" customWidth="1"/>
+    <col min="3" max="16384" width="11.44140625" style="8"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1693,33 +1687,33 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1728,115 +1722,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A9</f>
         <v>HorarioBarberia</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B9</f>
         <v>Entidad que registra, día por día, la hora de apertura y de cierre de la barbería, que es el límite dentro del cual debe caber el horario de cualquier barbero.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -1867,10 +1861,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1900,7 +1894,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -1916,9 +1910,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -1950,7 +1944,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -1963,15 +1957,15 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1994,7 +1988,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -2007,15 +2001,15 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2038,7 +2032,7 @@
         <v>29</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>28</v>
@@ -2051,15 +2045,15 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -2082,7 +2076,7 @@
         <v>29</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>28</v>
@@ -2095,15 +2089,15 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="12" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -2126,7 +2120,7 @@
         <v>29</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>28</v>
@@ -2139,10 +2133,10 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>104</v>
       </c>
@@ -2170,7 +2164,7 @@
         <v>29</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>28</v>
@@ -2183,29 +2177,29 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0900-000000000000}"/>
@@ -2217,33 +2211,33 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2252,20 +2246,20 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A10</f>
         <v>Bloqueo</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
@@ -2274,93 +2268,93 @@
         <f>Entidades!B10</f>
         <v>Entidad que registra los rangos de fecha y hora en los que un barbero no está disponible para atender sus citas.</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2391,10 +2385,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -2424,7 +2418,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -2440,9 +2434,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -2474,7 +2468,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -2487,15 +2481,15 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -2518,7 +2512,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -2531,15 +2525,15 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -2562,7 +2556,7 @@
         <v>29</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>28</v>
@@ -2575,29 +2569,29 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0A00-000000000000}"/>
@@ -2609,33 +2603,33 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -2644,115 +2638,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A11</f>
         <v>BarberoServicio</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B11</f>
         <v>Entidad asociativa que registra qué servicios sabe hacer cada barbero, cuánto tarda en realizarlos y cuánto tiempo extra reserva para ellos.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -2783,10 +2777,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -2816,7 +2810,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -2832,9 +2826,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -2866,7 +2860,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -2879,12 +2873,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -2916,7 +2910,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -2929,12 +2923,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>77</v>
@@ -2966,7 +2960,7 @@
         <v>29</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>28</v>
@@ -2975,12 +2969,12 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>77</v>
@@ -3012,7 +3006,7 @@
         <v>29</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>28</v>
@@ -3021,12 +3015,12 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="12" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>77</v>
@@ -3058,7 +3052,7 @@
         <v>29</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>28</v>
@@ -3067,10 +3061,10 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="12" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>104</v>
       </c>
@@ -3109,29 +3103,29 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="12" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0B00-000000000000}"/>
@@ -3143,33 +3137,33 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:T14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -3178,115 +3172,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A12</f>
         <v>HorarioBarbero</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="28.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B12</f>
         <v>Entidad que registra la jornada de trabajo de un barbero dentro de un horario de la barbería, con la hora en la que empieza, la hora en la que termina y su vigencia.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -3317,10 +3311,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -3350,7 +3344,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -3366,9 +3360,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -3400,7 +3394,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -3413,12 +3407,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -3450,7 +3444,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -3463,15 +3457,15 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -3494,7 +3488,7 @@
         <v>29</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>28</v>
@@ -3507,15 +3501,15 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -3538,7 +3532,7 @@
         <v>29</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>28</v>
@@ -3551,15 +3545,15 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -3593,15 +3587,15 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="12" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -3635,10 +3629,10 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="12" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>104</v>
       </c>
@@ -3677,29 +3671,29 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="12" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0C00-000000000000}"/>
@@ -3711,33 +3705,33 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -3746,20 +3740,20 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A13</f>
         <v>Agenda</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
@@ -3768,93 +3762,93 @@
         <f>Entidades!B13</f>
         <v>Entidad que representa el día concreto de trabajo de un barbero, según su horario, en el que se agrupan todas las citas de ese día.</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -3885,10 +3879,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -3918,7 +3912,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -3934,9 +3928,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -3968,7 +3962,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -3981,15 +3975,15 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -4012,7 +4006,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -4025,29 +4019,29 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0D00-000000000000}"/>
@@ -4059,33 +4053,33 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:T24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.5703125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.5546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -4094,115 +4088,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A14</f>
         <v>Cita</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B14</f>
         <v>Entidad que registra la reserva de un cliente con un barbero para una fecha y hora concretas, con su estado, los tiempos reales de la atención y el valor que debe pagar el cliente.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -4233,10 +4227,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -4266,7 +4260,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -4282,9 +4276,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -4315,7 +4309,9 @@
       <c r="L8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="M8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>185</v>
+      </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
       </c>
@@ -4327,12 +4323,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -4364,7 +4360,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -4377,12 +4373,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>27</v>
@@ -4425,15 +4421,15 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -4442,7 +4438,7 @@
         <v>28</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>28</v>
@@ -4456,7 +4452,7 @@
         <v>29</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>28</v>
@@ -4469,15 +4465,15 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -4511,15 +4507,15 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="12" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -4553,15 +4549,15 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="12" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -4595,15 +4591,15 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="12" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -4637,15 +4633,15 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="12" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -4679,12 +4675,12 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="12" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>77</v>
@@ -4716,7 +4712,7 @@
         <v>29</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P17" s="2" t="s">
         <v>28</v>
@@ -4725,12 +4721,12 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="12" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>77</v>
@@ -4762,7 +4758,7 @@
         <v>29</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>28</v>
@@ -4771,12 +4767,12 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>77</v>
@@ -4808,7 +4804,7 @@
         <v>29</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>28</v>
@@ -4817,12 +4813,12 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="12" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>77</v>
@@ -4854,7 +4850,7 @@
         <v>29</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>28</v>
@@ -4863,12 +4859,12 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="12" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>77</v>
@@ -4900,7 +4896,7 @@
         <v>29</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>28</v>
@@ -4909,12 +4905,12 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>77</v>
@@ -4928,7 +4924,7 @@
         <v>28</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>28</v>
@@ -4946,7 +4942,7 @@
         <v>29</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>28</v>
@@ -4955,12 +4951,12 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="12" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>77</v>
@@ -4974,7 +4970,7 @@
         <v>28</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>28</v>
@@ -4992,7 +4988,7 @@
         <v>29</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P23" s="2" t="s">
         <v>28</v>
@@ -5001,12 +4997,12 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="12" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>77</v>
@@ -5038,7 +5034,7 @@
         <v>29</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>28</v>
@@ -5047,29 +5043,29 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="12" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0E00-000000000000}"/>
@@ -5081,33 +5077,33 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.85546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.88671875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -5116,115 +5112,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A15</f>
         <v>CitaServicio</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B15</f>
         <v>Entidad asociativa que registra cada servicio incluido dentro de una cita, congelando el precio y la duración que tenía ese servicio para ese barbero en el momento de agendarla.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -5255,10 +5251,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -5288,7 +5284,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -5304,9 +5300,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -5338,7 +5334,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -5351,12 +5347,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -5388,7 +5384,7 @@
         <v>29</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>28</v>
@@ -5401,12 +5397,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>77</v>
@@ -5438,7 +5434,7 @@
         <v>29</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>28</v>
@@ -5447,12 +5443,12 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>77</v>
@@ -5484,7 +5480,7 @@
         <v>29</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="P11" s="2" t="s">
         <v>28</v>
@@ -5493,12 +5489,12 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="12" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>77</v>
@@ -5530,7 +5526,7 @@
         <v>29</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>28</v>
@@ -5539,12 +5535,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="12" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>77</v>
@@ -5576,7 +5572,7 @@
         <v>29</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="P13" s="2" t="s">
         <v>28</v>
@@ -5585,29 +5581,29 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0F00-000000000000}"/>
@@ -5619,33 +5615,33 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:T13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="40.140625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="40.109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -5654,115 +5650,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A16</f>
         <v>Multa</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B16</f>
         <v>Entidad que registra la sanción económica impuesta a un cliente por incumplir una cita, ya sea por tardanza o por inasistencia, con su monto y su estado de pago.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -5793,10 +5789,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -5826,7 +5822,7 @@
         <v>29</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>28</v>
@@ -5842,9 +5838,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>27</v>
@@ -5876,7 +5872,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>28</v>
@@ -5889,12 +5885,12 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="12" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>27</v>
@@ -5937,12 +5933,12 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="12" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>77</v>
@@ -5974,7 +5970,7 @@
         <v>29</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="P10" s="2" t="s">
         <v>28</v>
@@ -5983,15 +5979,15 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="12" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -6025,15 +6021,15 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="12" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -6067,12 +6063,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="12" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>81</v>
@@ -6109,29 +6105,29 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="12" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-1000-000000000000}"/>
@@ -6143,49 +6139,49 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C1" t="s">
         <v>39</v>
       </c>
       <c r="D1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>261</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
         <v>262</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>265</v>
       </c>
     </row>
   </sheetData>
@@ -6196,13 +6192,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="79" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
@@ -6210,7 +6206,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>37</v>
       </c>
@@ -6218,7 +6214,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>39</v>
       </c>
@@ -6226,7 +6222,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>41</v>
       </c>
@@ -6234,7 +6230,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>43</v>
       </c>
@@ -6242,7 +6238,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>45</v>
       </c>
@@ -6250,7 +6246,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>47</v>
       </c>
@@ -6258,7 +6254,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>49</v>
       </c>
@@ -6266,7 +6262,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>51</v>
       </c>
@@ -6274,7 +6270,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>53</v>
       </c>
@@ -6282,7 +6278,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>55</v>
       </c>
@@ -6290,7 +6286,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>57</v>
       </c>
@@ -6298,7 +6294,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>59</v>
       </c>
@@ -6306,7 +6302,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>61</v>
       </c>
@@ -6314,7 +6310,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>63</v>
       </c>
@@ -6322,7 +6318,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>65</v>
       </c>
@@ -6339,33 +6335,33 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:T8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="54.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="54.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -6374,115 +6370,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A2</f>
         <v>DiaSemana</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="38" t="str">
+      <c r="B3" s="24" t="str">
         <f>Entidades!B2</f>
         <v>Catálogo de los días de la semana, incluido festivo, que se usan para definir los horarios de la barbería y de cada barbero.</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
-      <c r="F4" s="35"/>
-      <c r="G4" s="35"/>
-      <c r="H4" s="35"/>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="35"/>
-      <c r="L4" s="35"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="35"/>
-      <c r="O4" s="35"/>
-      <c r="P4" s="35"/>
-      <c r="Q4" s="35"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="36"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
+      <c r="T4" s="20"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="35"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37" t="s">
+      <c r="J5" s="19"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="36"/>
-      <c r="N5" s="37" t="s">
+      <c r="M5" s="20"/>
+      <c r="N5" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="36"/>
-      <c r="P5" s="37" t="s">
+      <c r="O5" s="20"/>
+      <c r="P5" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="37" t="s">
+      <c r="Q5" s="19"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="37" t="s">
+      <c r="T5" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -6513,10 +6509,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="17"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>26</v>
       </c>
@@ -6562,7 +6558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -6610,10 +6606,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="P5:R5"/>
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="I5:K5"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
@@ -6628,6 +6620,10 @@
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="P5:R5"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="I5:K5"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -6639,33 +6635,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:T9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="45" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -6674,115 +6670,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A3</f>
         <v>Estado</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="28.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="28.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B3</f>
         <v>Catálogo de los estados en los que puede encontrarse una cita durante su ciclo de vida: agendada, finalizada, cancelada, con tardanza o con inasistencia.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -6813,10 +6809,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -6862,7 +6858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -6908,7 +6904,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>70</v>
       </c>
@@ -6954,24 +6950,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
@@ -6983,33 +6979,33 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:T11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42.28515625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="42.33203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -7018,115 +7014,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A4</f>
         <v>Servicio</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B4</f>
         <v>Entidad que almacena los servicios de corte y arreglo que ofrece la barbería, definidos por el dueño, y que luego cada barbero decide si los habilita.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -7157,10 +7153,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -7206,7 +7202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -7252,7 +7248,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -7296,7 +7292,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>76</v>
       </c>
@@ -7342,7 +7338,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>80</v>
       </c>
@@ -7386,24 +7382,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
@@ -7415,33 +7411,33 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="39.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="39.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -7450,34 +7446,34 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A5</f>
         <v>PrefijoCelular</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="38" t="str">
+      <c r="B3" s="24" t="str">
         <f>Entidades!B5</f>
         <v>Catálogo de prefijos telefónicos de país disponibles para el número de celular de barberos y clientes.</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="40"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="34" t="s">
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="21" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="42"/>
@@ -7500,57 +7496,57 @@
       <c r="S4" s="42"/>
       <c r="T4" s="42"/>
     </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37" t="s">
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="37" t="s">
+      <c r="D5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="37" t="s">
+      <c r="G5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="37" t="s">
+      <c r="I5" s="16" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="42"/>
       <c r="K5" s="42"/>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="16" t="s">
         <v>11</v>
       </c>
       <c r="M5" s="42"/>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="16" t="s">
         <v>12</v>
       </c>
       <c r="O5" s="42"/>
-      <c r="P5" s="37" t="s">
+      <c r="P5" s="16" t="s">
         <v>13</v>
       </c>
       <c r="Q5" s="42"/>
       <c r="R5" s="42"/>
-      <c r="S5" s="37" t="s">
+      <c r="S5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="37" t="s">
+      <c r="T5" s="16" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="42"/>
       <c r="B6" s="42"/>
       <c r="C6" s="42"/>
@@ -7592,7 +7588,7 @@
       <c r="S6" s="42"/>
       <c r="T6" s="42"/>
     </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -7638,7 +7634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>84</v>
       </c>
@@ -7684,27 +7680,27 @@
         <v>86</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
@@ -7716,33 +7712,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:T10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="33.5703125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="33.5546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -7751,20 +7747,20 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A6</f>
         <v>TipoMulta</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
@@ -7773,93 +7769,93 @@
         <f>Entidades!B6</f>
         <v>Catálogo de los tipos de multa que se le pueden imponer a un cliente: por tardanza o por inasistencia.</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -7890,10 +7886,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -7939,7 +7935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>32</v>
       </c>
@@ -7985,7 +7981,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -8029,27 +8025,27 @@
         <v>90</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
@@ -8061,33 +8057,33 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:T16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="29.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -8096,115 +8092,115 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A7</f>
         <v>Barbero</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="29.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
       </c>
-      <c r="B3" s="28" t="str">
+      <c r="B3" s="31" t="str">
         <f>Entidades!B7</f>
         <v>Entidad que almacena la información de los barberos que trabajan en la barbería, con su contacto, su vigencia y la anticipación mínima que exigen para que les agenden una cita.</v>
       </c>
-      <c r="C3" s="29"/>
-      <c r="D3" s="29"/>
-      <c r="E3" s="30"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="33"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -8235,10 +8231,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -8284,7 +8280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>92</v>
       </c>
@@ -8328,7 +8324,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -8372,7 +8368,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>96</v>
       </c>
@@ -8416,7 +8412,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>98</v>
       </c>
@@ -8460,7 +8456,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>84</v>
       </c>
@@ -8510,7 +8506,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -8556,7 +8552,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>104</v>
       </c>
@@ -8598,7 +8594,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>106</v>
       </c>
@@ -8607,7 +8603,7 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
@@ -8644,7 +8640,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>109</v>
       </c>
@@ -8692,24 +8688,24 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
@@ -8720,34 +8716,34 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:T16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="19.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:T15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="19.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="39.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="62.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="62.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="58.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="59.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="56.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="32.85546875" style="1" customWidth="1"/>
-    <col min="21" max="21" width="19.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="19.7109375" style="1"/>
+    <col min="5" max="5" width="39.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="62.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="62.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="58.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="59.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="56.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="32.88671875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="19.6640625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="19.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -8756,20 +8752,20 @@
       <c r="D1" s="23"/>
       <c r="E1" s="23"/>
     </row>
-    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="str">
         <f>Entidades!$A$1</f>
         <v>Entidad</v>
       </c>
-      <c r="B2" s="25" t="str">
+      <c r="B2" s="27" t="str">
         <f>Entidades!A8</f>
         <v>Cliente</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="20"/>
-    </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="29"/>
+    </row>
+    <row r="3" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="str">
         <f>Entidades!$B$1</f>
         <v>Desripción</v>
@@ -8778,93 +8774,93 @@
         <f>Entidades!B8</f>
         <v>Entidad que almacena la información de los clientes que solicitan citas en la barbería, junto con sus multas sin pagar y su estado de veto.</v>
       </c>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="36"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
-      <c r="H4" s="17"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
-      <c r="N4" s="17"/>
-      <c r="O4" s="17"/>
-      <c r="P4" s="17"/>
-      <c r="Q4" s="17"/>
-      <c r="R4" s="17"/>
-      <c r="S4" s="17"/>
-      <c r="T4" s="18"/>
-    </row>
-    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38"/>
+      <c r="R4" s="38"/>
+      <c r="S4" s="38"/>
+      <c r="T4" s="39"/>
+    </row>
+    <row r="5" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="19" t="s">
+      <c r="G5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="33" t="s">
+      <c r="H5" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="19" t="s">
+      <c r="I5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="J5" s="21"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="19" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="M5" s="20"/>
-      <c r="N5" s="19" t="s">
+      <c r="M5" s="29"/>
+      <c r="N5" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O5" s="20"/>
-      <c r="P5" s="19" t="s">
+      <c r="O5" s="29"/>
+      <c r="P5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="21"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="19" t="s">
+      <c r="Q5" s="28"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="T5" s="26" t="s">
+      <c r="T5" s="40" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="32"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
+    <row r="6" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
       <c r="I6" s="6" t="s">
         <v>16</v>
       </c>
@@ -8895,10 +8891,10 @@
       <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="S6" s="24"/>
-      <c r="T6" s="27"/>
-    </row>
-    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+      <c r="S6" s="17"/>
+      <c r="T6" s="41"/>
+    </row>
+    <row r="7" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
@@ -8944,7 +8940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>92</v>
       </c>
@@ -8988,7 +8984,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>94</v>
       </c>
@@ -9032,7 +9028,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>96</v>
       </c>
@@ -9076,7 +9072,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>98</v>
       </c>
@@ -9120,7 +9116,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>117</v>
       </c>
@@ -9170,7 +9166,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -9216,7 +9212,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>121</v>
       </c>
@@ -9258,17 +9254,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="2">
-        <v>1</v>
-      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
         <v>28</v>
@@ -9289,11 +9283,9 @@
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>124</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" s="2" t="s">
         <v>28</v>
       </c>
@@ -9301,75 +9293,195 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="12" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="H5:H6"/>
     <mergeCell ref="P5:R5"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="N5:O5"/>
     <mergeCell ref="I5:K5"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="S5:S6"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="L5:M5"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="T5:T6"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="G5:G6"/>
     <mergeCell ref="E5:E6"/>
-    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="H5:H6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" location="Entidades!A1" tooltip="Volver al inicio" display="&lt;-Volver al inicio" xr:uid="{00000000-0004-0000-0800-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100BCA4BE53A4AA0F4CB08FF25AA3B9819F" ma:contentTypeVersion="0" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="3e9a29a193e387f43749495b8c596a54">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="26ff3a126252e742cc2543983a566b0e">
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all/>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D36BC523-885B-4F46-9DF9-93A276E90171}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A44E1E22-D840-4131-A173-816AD6E818A6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{096442F7-EB67-48B3-8780-943637A2FDD2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>